--- a/game_config/Datas/__tables__.xlsx
+++ b/game_config/Datas/__tables__.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>地图配置</t>
+          <t>地图冷配置</t>
         </is>
       </c>
     </row>
@@ -697,6 +697,126 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>玩家基础配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>game.TbAoiConfig</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AoiConfig</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AoiConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AOI可见性冷配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>game.TbAoiSyncTierConfig</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AoiSyncTierConfig</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AoiSyncTierConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AOI同步层级冷配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>game.TbConfigTablePolicy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ConfigTablePolicy</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ConfigTablePolicy.xlsx</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>table_name</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>配置表冷热策略</t>
         </is>
       </c>
     </row>

--- a/game_config/Datas/__tables__.xlsx
+++ b/game_config/Datas/__tables__.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -820,6 +820,86 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>game.TbMonsterConfig</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MonsterConfig</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MonsterConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>怪物模板配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>game.TbMonsterAreaConfig</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MonsterAreaConfig</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MonsterAreaConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>怪物固定刷点配置</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/game_config/Datas/__tables__.xlsx
+++ b/game_config/Datas/__tables__.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -900,6 +900,46 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>game.TbBuffConfig</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BuffConfig</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BuffConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Buff配置</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/game_config/Datas/__tables__.xlsx
+++ b/game_config/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D250021-7C36-423C-A2AE-D8ABB96B87A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1524F632-20EE-446F-82AA-A85D2242315D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
   <si>
     <t>##var</t>
   </si>
@@ -262,6 +262,30 @@
   <si>
     <t>技能有序效果配置</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>game.TbQuestConfig</t>
+  </si>
+  <si>
+    <t>QuestConfig</t>
+  </si>
+  <si>
+    <t>QuestConfig.xlsx</t>
+  </si>
+  <si>
+    <t>任务配置</t>
+  </si>
+  <si>
+    <t>game.TbQuestObjectiveConfig</t>
+  </si>
+  <si>
+    <t>QuestObjectiveConfig</t>
+  </si>
+  <si>
+    <t>QuestObjectiveConfig.xlsx</t>
+  </si>
+  <si>
+    <t>任务目标配置</t>
   </si>
 </sst>
 </file>
@@ -635,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
@@ -1022,6 +1046,58 @@
         <v>74</v>
       </c>
     </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/game_config/Datas/__tables__.xlsx
+++ b/game_config/Datas/__tables__.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -217,51 +217,39 @@
   </si>
   <si>
     <t>game.TbSkillConfig</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillConfig</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillConfig.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>map</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>c,s</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能施法规则配置</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>game.TbSkillEffectConfig</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffectConfig</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffectConfig.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>s</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能有序效果配置</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>game.TbQuestConfig</t>
@@ -286,6 +274,18 @@
   </si>
   <si>
     <t>任务目标配置</t>
+  </si>
+  <si>
+    <t>game.TbDropTableConfig</t>
+  </si>
+  <si>
+    <t>DropTableConfig</t>
+  </si>
+  <si>
+    <t>DropTableConfig.xlsx</t>
+  </si>
+  <si>
+    <t>掉落表配置</t>
   </si>
 </sst>
 </file>
@@ -659,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
@@ -1098,6 +1098,32 @@
         <v>82</v>
       </c>
     </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
